--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C723BE-42E4-4B1D-B567-62DF56FC4F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCEB69B-AC30-42AF-A905-A48C21E80CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,6 +122,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -153,18 +159,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,58 +493,60 @@
   <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="6"/>
-    <col min="2" max="2" width="38.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.46484375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="4" customWidth="1"/>
-    <col min="5" max="7" width="10.86328125" style="4" customWidth="1"/>
-    <col min="8" max="11" width="23.06640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.59765625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.06640625" style="4"/>
+    <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
+    <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
+    <col min="8" max="11" width="23.06640625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="21.59765625" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCEB69B-AC30-42AF-A905-A48C21E80CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CB0C6A-5B4F-4356-8183-736836B7348D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Appreciation" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CB0C6A-5B4F-4356-8183-736836B7348D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D66BC6D-BB11-482D-82AA-59139E081B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Appreciation" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Date From</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>Distribution Place</t>
-  </si>
-  <si>
-    <t>Distribution Date</t>
   </si>
   <si>
     <t>Gender</t>
@@ -112,7 +109,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,12 +119,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -159,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -175,7 +166,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="4"/>
@@ -500,11 +490,10 @@
     <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
     <col min="8" max="11" width="23.06640625" style="5" customWidth="1"/>
     <col min="12" max="12" width="22.33203125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="21.59765625" style="5" customWidth="1"/>
-    <col min="14" max="16384" width="9.06640625" style="6"/>
+    <col min="13" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -530,19 +519,16 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D66BC6D-BB11-482D-82AA-59139E081B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF87B936-920F-48BB-A2C3-42DB86165B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -532,6 +532,30 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the scope." sqref="E2:E1048576" xr:uid="{55D4437E-4502-4429-8E28-8300D371431A}">
+      <formula1>46023</formula1>
+      <formula2>46752</formula2>
+    </dataValidation>
+    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="G2:G1048576" xr:uid="{96321B9C-3BE2-45C5-BA8E-E454BE7A33D8}">
+      <formula1>0.208333333333333</formula1>
+      <formula2>0.833333333333333</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="I2:I1048576" xr:uid="{B0F3A25E-6FCA-4EC0-8F9C-FBC2F93C6E48}">
+      <formula1>"Male, Female"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid unit." sqref="A2:A1048576" xr:uid="{07239DD4-CBA6-46B8-BBF6-77B43EA4F703}">
+      <formula1>"AGRISTAT, AMIA, DRRM"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the scope." sqref="D2:D1048576" xr:uid="{285FB07D-F8DC-49B0-90A8-B30E1CF1E553}">
+      <formula1>46023</formula1>
+      <formula2>46752</formula2>
+    </dataValidation>
+    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="F2:F1048576" xr:uid="{280D15D6-C39E-472B-8FA3-A9B39C202048}">
+      <formula1>0.208333333333333</formula1>
+      <formula2>0.833333333333333</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF87B936-920F-48BB-A2C3-42DB86165B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D151B4E-8983-4367-8FD8-54D6FEB3A72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Date From</t>
   </si>
@@ -55,12 +55,6 @@
   </si>
   <si>
     <t>Unit</t>
-  </si>
-  <si>
-    <t>Time Start</t>
-  </si>
-  <si>
-    <t>Time End</t>
   </si>
   <si>
     <t>Distribution Place</t>
@@ -480,20 +474,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="4"/>
     <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
-    <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
-    <col min="8" max="11" width="23.06640625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="9.06640625" style="6"/>
+    <col min="5" max="5" width="10.86328125" style="5" customWidth="1"/>
+    <col min="6" max="9" width="23.06640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -509,51 +503,33 @@
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the scope." sqref="E2:E1048576" xr:uid="{55D4437E-4502-4429-8E28-8300D371431A}">
+  <dataValidations count="3">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the scope." sqref="D2:E1048576" xr:uid="{55D4437E-4502-4429-8E28-8300D371431A}">
       <formula1>46023</formula1>
       <formula2>46752</formula2>
     </dataValidation>
-    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="G2:G1048576" xr:uid="{96321B9C-3BE2-45C5-BA8E-E454BE7A33D8}">
-      <formula1>0.208333333333333</formula1>
-      <formula2>0.833333333333333</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="I2:I1048576" xr:uid="{B0F3A25E-6FCA-4EC0-8F9C-FBC2F93C6E48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="G2:G1048576" xr:uid="{B0F3A25E-6FCA-4EC0-8F9C-FBC2F93C6E48}">
       <formula1>"Male, Female"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid unit." sqref="A2:A1048576" xr:uid="{07239DD4-CBA6-46B8-BBF6-77B43EA4F703}">
       <formula1>"AGRISTAT, AMIA, DRRM"</formula1>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the scope." sqref="D2:D1048576" xr:uid="{285FB07D-F8DC-49B0-90A8-B30E1CF1E553}">
-      <formula1>46023</formula1>
-      <formula2>46752</formula2>
-    </dataValidation>
-    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="F2:F1048576" xr:uid="{280D15D6-C39E-472B-8FA3-A9B39C202048}">
-      <formula1>0.208333333333333</formula1>
-      <formula2>0.833333333333333</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D151B4E-8983-4367-8FD8-54D6FEB3A72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886256BF-980E-4223-B0AA-450B2BBD1204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>Destination</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>Distribution Place</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
   </si>
   <si>
     <t>Office</t>
+  </si>
+  <si>
+    <t>Assignment</t>
   </si>
 </sst>
 </file>
@@ -477,7 +477,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="4"/>
+    <col min="1" max="1" width="11.53125" style="4" customWidth="1"/>
     <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
@@ -489,7 +489,7 @@
   <sheetData>
     <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -507,16 +507,16 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886256BF-980E-4223-B0AA-450B2BBD1204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8CAFC4-9760-4661-BE03-415BFA7449EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -66,7 +66,7 @@
     <t>Office</t>
   </si>
   <si>
-    <t>Assignment</t>
+    <t>Certificate Template From</t>
   </si>
 </sst>
 </file>
@@ -103,7 +103,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,6 +113,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,13 +156,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -159,6 +169,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,18 +499,17 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.53125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" style="5" customWidth="1"/>
-    <col min="6" max="9" width="23.06640625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="9.06640625" style="6"/>
+    <col min="1" max="1" width="35.59765625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="35.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" style="3" customWidth="1"/>
+    <col min="6" max="9" width="23.06640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -497,25 +518,25 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
     </row>

--- a/public/Appreciation_Importing_Template.xlsx
+++ b/public/Appreciation_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8CAFC4-9760-4661-BE03-415BFA7449EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371AA787-A205-41D7-B74F-E41A2CE3AB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -161,12 +161,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -181,6 +175,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,17 +499,17 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.59765625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="35.59765625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" style="3" customWidth="1"/>
-    <col min="6" max="9" width="23.06640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.06640625" style="4"/>
+    <col min="1" max="1" width="35.59765625" style="7" customWidth="1"/>
+    <col min="2" max="3" width="35.59765625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" style="8" customWidth="1"/>
+    <col min="6" max="9" width="23.06640625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="8" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -524,19 +524,19 @@
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
